--- a/artfynd/A 68883-2021 artfynd.xlsx
+++ b/artfynd/A 68883-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 68883-2021 artfynd.xlsx
+++ b/artfynd/A 68883-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>60505106</v>
+        <v>425325</v>
       </c>
       <c r="B2" t="n">
-        <v>96367</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219874</v>
+        <v>1760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Kvällsmaskros</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Taraxacum praestans</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+          <t>H. Lindb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Västergården NV om, Srm</t>
+          <t>Ornö, Västergården, 350-400 m NNO N-aste bonhus (*kvällsmaskros* /plant/) , Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>696161.9228651687</v>
+        <v>696202</v>
       </c>
       <c r="R2" t="n">
-        <v>6553221.288343124</v>
+        <v>6553359</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,24 +747,24 @@
           <t>Ornö</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>AB-Han-0003</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-06-11</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2005-06-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-06-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2005-06-06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Minst 2 ex. Även samlad vid koordinaten 6553293, 1650176</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,25 +778,908 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Hävdad ängsmark</t>
-        </is>
-      </c>
+          <t>betad friskäng</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>Anders Svenson</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Anders Svenson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Anders Svenson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>60505091</v>
+      </c>
+      <c r="B3" t="n">
+        <v>111390</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Västergården NV om, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>696216</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6553407</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2016-06-11</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2016-06-11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>I knopp också.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Buskrik ängsmark</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Jan Yngve Andersson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Jan Yngve Andersson, Rolf Wahlström, Göran Frisk, Karin HL Bergendal, Ann Sjölander, Yolanda Karlsson, Kerstin Frostberg, Henry Gudmundson, Lillebil Norden, Linda Irebrand, solveig raaschou, Eva Grönlund, Bo Reichenberg, Bo Ljungberg, Bengt Hellman</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>BSIS - Floraväkteri-exkursion</t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>60505093</v>
+      </c>
+      <c r="B4" t="n">
+        <v>111390</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Västergården NV om, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>696210</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6553403</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2016-06-11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2016-06-11</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Buskrik ängsmark</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson, Rolf Wahlström, Göran Frisk, Karin HL Bergendal, Ann Sjölander, Yolanda Karlsson, Kerstin Frostberg, Henry Gudmundson, Lillebil Norden, Linda Irebrand, solveig raaschou, Eva Grönlund, Bo Reichenberg, Bo Ljungberg, Bengt Hellman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>BSIS - Floraväkteri-exkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>60505106</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Västergården NV om, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>696162</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6553221</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2016-06-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2016-06-11</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Hävdad ängsmark</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson, Rolf Wahlström, Göran Frisk, Karin HL Bergendal, Ann Sjölander, Yolanda Karlsson, Kerstin Frostberg, Henry Gudmundson, Lillebil Norden, Linda Irebrand, solveig raaschou, Eva Grönlund, Bo Reichenberg, Bo Ljungberg, Bengt Hellman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>BSIS - Floraväkteri-exkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2672620</v>
+      </c>
+      <c r="B6" t="n">
+        <v>109815</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ornö, N Västergården, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>696100</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6553119</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2006-06-29</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2006-06-29</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Storvägslänt</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Henry Gudmundson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Henry Gudmundson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>60505089</v>
+      </c>
+      <c r="B7" t="n">
+        <v>109815</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Västergården NV om, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>696227</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6553411</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2016-06-11</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2016-06-11</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Buskrik ängsmark</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson, Rolf Wahlström, Göran Frisk, Karin HL Bergendal, Ann Sjölander, Yolanda Karlsson, Kerstin Frostberg, Henry Gudmundson, Lillebil Norden, Linda Irebrand, solveig raaschou, Eva Grönlund, Bo Reichenberg, Bo Ljungberg, Bengt Hellman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>BSIS - Floraväkteri-exkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>60505100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Västergården NV om, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>696154</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6553267</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2016-06-11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2016-06-11</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Hävdad ängsmark</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson, Rolf Wahlström, Göran Frisk, Karin HL Bergendal, Ann Sjölander, Yolanda Karlsson, Kerstin Frostberg, Henry Gudmundson, Lillebil Norden, Linda Irebrand, solveig raaschou, Eva Grönlund, Bo Reichenberg, Bo Ljungberg, Bengt Hellman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>BSIS - Floraväkteri-exkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>60505105</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Västergården NV om, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>696161</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6553231</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2016-06-11</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2016-06-11</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Hävdad ängsmark</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson, Rolf Wahlström, Göran Frisk, Karin HL Bergendal, Ann Sjölander, Yolanda Karlsson, Kerstin Frostberg, Henry Gudmundson, Lillebil Norden, Linda Irebrand, solveig raaschou, Eva Grönlund, Bo Reichenberg, Bo Ljungberg, Bengt Hellman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>BSIS - Floraväkteri-exkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6000847</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99154</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>223619</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ängsnattviol</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. bifolia</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ornö, N Västergården, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>696100</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6553119</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2006-06-29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2006-06-29</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Storvägkant</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Henry Gudmundson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Henry Gudmundson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 68883-2021 artfynd.xlsx
+++ b/artfynd/A 68883-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -803,6 +808,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/425325</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -919,6 +929,11 @@
           <t>BSIS - Floraväkteri-exkursion</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60505091</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1030,6 +1045,11 @@
           <t>BSIS - Floraväkteri-exkursion</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60505093</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1141,6 +1161,11 @@
           <t>BSIS - Floraväkteri-exkursion</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60505106</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1248,6 +1273,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2672620</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1359,6 +1389,11 @@
           <t>BSIS - Floraväkteri-exkursion</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60505089</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1470,6 +1505,11 @@
           <t>BSIS - Floraväkteri-exkursion</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60505100</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1577,6 +1617,11 @@
           <t>BSIS - Floraväkteri-exkursion</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60505105</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1680,8 +1725,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6000847</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>